--- a/Chicos.xlsx
+++ b/Chicos.xlsx
@@ -8,15 +8,15 @@
   </sheets>
   <definedNames>
     <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Hoja 1'!$A$1:$A$1000</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_ECF8F012_2E7F_4858_BEE0_5CA922680290_.wvu.FilterData">'Hoja 1'!$C$2:$C$94</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_90464501_1BCD_407B_BACB_143FAAC96C43_.wvu.FilterData">'Hoja 1'!$C$1:$C$94</definedName>
-    <definedName hidden="1" localSheetId="0" name="Z_A31490EF_22C8_44A4_BD6A_3C31E821B0E9_.wvu.FilterData">'Hoja 1'!$C$2:$C$94</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_D495C9E0_2396_4B6E_9922_C5AA8E6FB1B2_.wvu.FilterData">'Hoja 1'!$C$2:$C$94</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_5A096350_A62D_4CB1_90A2_9B6B1A6010D6_.wvu.FilterData">'Hoja 1'!$C$2:$C$94</definedName>
+    <definedName hidden="1" localSheetId="0" name="Z_E7DE329C_7481_4D41_8A65_E791231BC72A_.wvu.FilterData">'Hoja 1'!$C$1:$C$94</definedName>
   </definedNames>
   <calcPr/>
   <customWorkbookViews>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{90464501-1BCD-407B-BACB-143FAAC96C43}" name="Unis"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{A31490EF-22C8-44A4-BD6A-3C31E821B0E9}" name="Filtro 1"/>
-    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{ECF8F012-2E7F-4858-BEE0-5CA922680290}" name="Filtro 2"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{E7DE329C-7481-4D41-8A65-E791231BC72A}" name="Unis"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{5A096350-A62D-4CB1-90A2-9B6B1A6010D6}" name="Filtro 1"/>
+    <customWorkbookView activeSheetId="0" maximized="1" windowHeight="0" windowWidth="0" guid="{D495C9E0-2396-4B6E-9922-C5AA8E6FB1B2}" name="Filtro 2"/>
   </customWorkbookViews>
 </workbook>
 </file>
@@ -8677,21 +8677,21 @@
     </sortState>
   </autoFilter>
   <customSheetViews>
-    <customSheetView guid="{ECF8F012-2E7F-4858-BEE0-5CA922680290}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{D495C9E0-2396-4B6E-9922-C5AA8E6FB1B2}" filter="1" showAutoFilter="1">
       <autoFilter ref="$C$2:$C$94">
         <sortState ref="C2:C94">
           <sortCondition ref="C2:C94"/>
         </sortState>
       </autoFilter>
     </customSheetView>
-    <customSheetView guid="{A31490EF-22C8-44A4-BD6A-3C31E821B0E9}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{5A096350-A62D-4CB1-90A2-9B6B1A6010D6}" filter="1" showAutoFilter="1">
       <autoFilter ref="$C$2:$C$94">
         <sortState ref="C2:C94">
           <sortCondition ref="C2:C94"/>
         </sortState>
       </autoFilter>
     </customSheetView>
-    <customSheetView guid="{90464501-1BCD-407B-BACB-143FAAC96C43}" filter="1" showAutoFilter="1">
+    <customSheetView guid="{E7DE329C-7481-4D41-8A65-E791231BC72A}" filter="1" showAutoFilter="1">
       <autoFilter ref="$C$1:$C$94">
         <sortState ref="C1:C94">
           <sortCondition ref="C1:C94"/>
